--- a/cds/mm_ireland-5year-cds.xlsx
+++ b/cds/mm_ireland-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="508">
   <si>
     <t>Date</t>
   </si>
@@ -1524,6 +1524,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1888,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5890,6 +5905,46 @@
       </c>
       <c r="B502" s="3">
         <v>16.3515</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B503" s="3">
+        <v>16.2708</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B504" s="3">
+        <v>16.9116</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B505" s="3">
+        <v>18.5999</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B506" s="3">
+        <v>18.7057</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B507" s="3">
+        <v>18.1746</v>
       </c>
     </row>
   </sheetData>
